--- a/travel/2026-11_JFM-GRIPS_survey/学会出席等出張許可申請書_11月13日_相模原調査.xlsx
+++ b/travel/2026-11_JFM-GRIPS_survey/学会出席等出張許可申請書_11月13日_相模原調査.xlsx
@@ -1868,7 +1868,7 @@
         <v>3</v>
       </c>
       <c r="Y2" s="8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z2" s="7" t="s">
         <v>4</v>
